--- a/Assessment Questions/AIE/BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.xlsx
+++ b/Assessment Questions/AIE/BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface Tour, Data visualizat" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -429,12 +424,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Type</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
         </is>
       </c>
     </row>
@@ -444,12 +474,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>What is Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart within Tableau Fundamentals?</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -459,12 +494,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Why is Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart important in practice?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -474,12 +514,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Explain the core concepts involved in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -489,12 +534,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Describe a simple workflow or process for Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -504,12 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>What tools, methods, or metrics are commonly used in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -519,12 +574,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>What common challenges or mistakes should be avoided in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -534,12 +594,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>How would you evaluate the quality or success of work done in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Theory</t>
         </is>
       </c>
     </row>
@@ -549,12 +614,377 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Give a practical business or technical use case for Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Theory</t>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Why is Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart important in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Explain the main workflow of Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Process Understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>List the key components involved in Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Component Awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How is Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart applied in a practical business scenario?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Applied Understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What problem does Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart help solve?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Problem Framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe the core steps required to complete Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Execution Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>What inputs are typically required before starting Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Input Readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What outputs or results are expected from Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Output Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>How would you validate whether Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart was completed correctly?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What are common mistakes to avoid while working on Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Error Awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How does Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart improve decision-making or outcomes?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Tableau Fundamentals/Interface Tour, Data visualization_ Pie chart, Column chart, Bar chart</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Business Value</t>
         </is>
       </c>
     </row>
